--- a/artfynd/A 11755-2023 artfynd.xlsx
+++ b/artfynd/A 11755-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131281611</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11755-2023 artfynd.xlsx
+++ b/artfynd/A 11755-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131281611</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11755-2023 artfynd.xlsx
+++ b/artfynd/A 11755-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131281611</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11755-2023 artfynd.xlsx
+++ b/artfynd/A 11755-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131281611</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11755-2023 artfynd.xlsx
+++ b/artfynd/A 11755-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131281611</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11755-2023 artfynd.xlsx
+++ b/artfynd/A 11755-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131281611</v>
       </c>
       <c r="B2" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11755-2023 artfynd.xlsx
+++ b/artfynd/A 11755-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131281611</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11755-2023 artfynd.xlsx
+++ b/artfynd/A 11755-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131281611</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11755-2023 artfynd.xlsx
+++ b/artfynd/A 11755-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131281611</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11755-2023 artfynd.xlsx
+++ b/artfynd/A 11755-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131281611</v>
+        <v>131281558</v>
       </c>
       <c r="B2" t="n">
-        <v>57901</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stenmossen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485808</v>
+        <v>485858</v>
       </c>
       <c r="R2" t="n">
-        <v>6673115</v>
+        <v>6673006</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +779,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131281611</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stenmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>485808</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6673115</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
